--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:39</t>
+    <t xml:space="preserve">2026-09-10 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:47</t>
+    <t xml:space="preserve">2026-09-18 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:56</t>
+    <t xml:space="preserve">2026-09-23 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,9 @@
       <c r="C10" s="2" t="n">
         <v>2302</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E10" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:16</t>
+    <t xml:space="preserve">2026-10-02 15:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:29</t>
+    <t xml:space="preserve">2026-10-05 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
